--- a/Createur/New_File3.xlsx
+++ b/Createur/New_File3.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>aaroonnn</t>
+          <t>Aaron</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kurraikkirrtu</t>
+          <t>baixa</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kurraikkirrtu</t>
+          <t>baixant</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>taallltt</t>
+          <t>abaixar</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kaivittu</t>
+          <t>abandonar</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kaivittutl</t>
+          <t>abandonant</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kaivittpptttttu</t>
+          <t>abandonat</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kaivittpptttttu</t>
+          <t>abandonat</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kaivittppttttvr</t>
+          <t>abandonat</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kaivittppttttvrkll</t>
+          <t>abandonats</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vittttuvittu</t>
+          <t>renunciar</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vittttuvittu</t>
+          <t>renunciar</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kaivittu</t>
+          <t>abandonar</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>apee</t>
+          <t>abadia</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tikaittaar</t>
+          <t>atordit</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tikaippu</t>
+          <t>aturdir</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tikaippu</t>
+          <t>desconcert</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>villkku nillll</t>
+          <t>pantalla de llum</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>irraicci kuuttngkll</t>
+          <t>abats</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pttukolai</t>
+          <t>matanca</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vettttupvr</t>
+          <t>talador</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>irraicci kuuttm</t>
+          <t>escorxador</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>villlunttu</t>
+          <t>va caure</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>attittaarkll</t>
+          <t>colpejat</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pttukolai ceyyppttttaar</t>
+          <t>sacrificat</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>apee</t>
+          <t>abadia</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>apee</t>
+          <t>abadia</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>apee</t>
+          <t>abat</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>apees</t>
+          <t>abadessa</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eepici</t>
+          <t>abc</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>apcettr</t>
+          <t>Abceder</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ciilll</t>
+          <t>absces</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>aptel</t>
+          <t>Abdel</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>turrvu</t>
+          <t>abdicacio</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>turrvu</t>
+          <t>abdicar</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vyirru</t>
+          <t>abdomen</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>vyirru</t>
+          <t>abdominal</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>apeecittaiyr</t>
+          <t>abecedaire</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>teennnii</t>
+          <t>abella</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>aannnaalum</t>
+          <t>pero</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>maarruptttt</t>
+          <t>aberrant</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pirrlllvu</t>
+          <t>aberracio</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>uukkm</t>
+          <t>abetir</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>verruppvr</t>
+          <t>aborridor</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>apittjnnn</t>
+          <t>Abidjan</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pllllm</t>
+          <t>avenc</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ceetm</t>
+          <t>dany</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kiilllttrmaannn</t>
+          <t>abjecte</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aruvruppu</t>
+          <t>abjeccio</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kaivittu</t>
+          <t>abjurar</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>niikkutl</t>
+          <t>ablacio</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pttttai</t>
+          <t>escorca</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>olllikkpptttttu</t>
+          <t>abolit</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>olllikk</t>
+          <t>abolir</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>olllittl</t>
+          <t>abolicio</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>olllippuvaatm</t>
+          <t>abolicionisme</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>olllippuvaati</t>
+          <t>abolicionista</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>aruvruppu</t>
+          <t>abominacio</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>aruvruppaannnvr</t>
+          <t>abominer</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eeraallmaak</t>
+          <t>abundantment</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>mikutiyaak</t>
+          <t>abundancia</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>eeraallmaannn</t>
+          <t>abundants</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eeraallmaannn</t>
+          <t>abundants</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cntaataarr</t>
+          <t>subscriptor</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>cntaataarr</t>
+          <t>subscriptor</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cntaa</t>
+          <t>subscripcio</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cntaakkll</t>
+          <t>subscripcions</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ptivu</t>
+          <t>subscriu-te</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>cntaakkll</t>
+          <t>subscripcions</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>kpplil</t>
+          <t>a bord</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>mlivu</t>
+          <t>assequible</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>mootl</t>
+          <t>col*lisio</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>mukvrikll</t>
+          <t>adreces</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>mukvrikll</t>
+          <t>adreces</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>traiyirrkk</t>
+          <t>aterrar</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>annukinnnaar</t>
+          <t>es va apropar</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>currrriyullll</t>
+          <t>entorns</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>plllngkuttiyinnnr</t>
+          <t>aborigen</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>plllngkuttiyinnnr</t>
+          <t>aborigens</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>krukklaippu</t>
+          <t>avortat</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>prrrri</t>
+          <t>Sobre</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>verrrrikrmaannn</t>
+          <t>reeixit</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>attaiy</t>
+          <t>aconseguir</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>villaivikkum</t>
+          <t>resultaria</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>villaivu</t>
+          <t>resultat</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>villaivaak</t>
+          <t>resultat</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>villaivaak</t>
+          <t>resultant</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kurraikk</t>
+          <t>bordar</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kcppaannn</t>
+          <t>abracadabrant</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ciraayppu</t>
+          <t>abrasiu</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ciraayppu</t>
+          <t>abrasio</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ciraayppu</t>
+          <t>abrasiu</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>curukkvum</t>
+          <t>abreujar</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>oppu</t>
+          <t>abreujat</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>pirippvr</t>
+          <t>abreger</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>tnnnniirukku</t>
+          <t>regar</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>curukkm</t>
+          <t>abreviatura</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>curukkngkll</t>
+          <t>abreviatures</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>tngkumittm</t>
+          <t>refugi</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>paataami plllm</t>
+          <t>albercoc</t>
         </is>
       </c>
     </row>
